--- a/Team-Data/2013-14/1-28-2013-14.xlsx
+++ b/Team-Data/2013-14/1-28-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>1</v>
       </c>
       <c r="AD2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
@@ -778,7 +845,7 @@
         <v>24</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR2" t="n">
         <v>27</v>
@@ -793,22 +860,22 @@
         <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AW2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX2" t="n">
         <v>22</v>
       </c>
       <c r="AY2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB2" t="n">
         <v>12</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-28-2013-14</t>
+          <t>2014-01-28</t>
         </is>
       </c>
     </row>
@@ -843,28 +910,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E3" t="n">
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G3" t="n">
-        <v>0.319</v>
+        <v>0.326</v>
       </c>
       <c r="H3" t="n">
         <v>48.1</v>
       </c>
       <c r="I3" t="n">
-        <v>36.1</v>
+        <v>36.2</v>
       </c>
       <c r="J3" t="n">
         <v>82.8</v>
       </c>
       <c r="K3" t="n">
-        <v>0.436</v>
+        <v>0.437</v>
       </c>
       <c r="L3" t="n">
         <v>6.3</v>
@@ -873,13 +940,13 @@
         <v>19.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0.325</v>
+        <v>0.326</v>
       </c>
       <c r="O3" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="P3" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="Q3" t="n">
         <v>0.767</v>
@@ -903,7 +970,7 @@
         <v>7.1</v>
       </c>
       <c r="X3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y3" t="n">
         <v>4.5</v>
@@ -915,25 +982,25 @@
         <v>18.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>94.59999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>-4.4</v>
+        <v>-3.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="n">
         <v>26</v>
       </c>
       <c r="AF3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG3" t="n">
         <v>27</v>
       </c>
       <c r="AH3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI3" t="n">
         <v>24</v>
@@ -948,7 +1015,7 @@
         <v>25</v>
       </c>
       <c r="AM3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN3" t="n">
         <v>28</v>
@@ -957,19 +1024,19 @@
         <v>25</v>
       </c>
       <c r="AP3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR3" t="n">
         <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU3" t="n">
         <v>29</v>
@@ -981,7 +1048,7 @@
         <v>24</v>
       </c>
       <c r="AX3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY3" t="n">
         <v>11</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-28-2013-14</t>
+          <t>2014-01-28</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AE4" t="n">
         <v>18</v>
@@ -1163,7 +1230,7 @@
         <v>17</v>
       </c>
       <c r="AX4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY4" t="n">
         <v>8</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-28-2013-14</t>
+          <t>2014-01-28</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-3.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE5" t="n">
         <v>19</v>
@@ -1318,7 +1385,7 @@
         <v>20</v>
       </c>
       <c r="AO5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP5" t="n">
         <v>9</v>
@@ -1336,7 +1403,7 @@
         <v>23</v>
       </c>
       <c r="AU5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV5" t="n">
         <v>2</v>
@@ -1360,7 +1427,7 @@
         <v>28</v>
       </c>
       <c r="BC5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-28-2013-14</t>
+          <t>2014-01-28</t>
         </is>
       </c>
     </row>
@@ -1467,10 +1534,10 @@
         <v>-0.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF6" t="n">
         <v>15</v>
@@ -1509,13 +1576,13 @@
         <v>8</v>
       </c>
       <c r="AR6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS6" t="n">
         <v>9</v>
       </c>
       <c r="AT6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AU6" t="n">
         <v>13</v>
@@ -1524,7 +1591,7 @@
         <v>26</v>
       </c>
       <c r="AW6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX6" t="n">
         <v>8</v>
@@ -1542,7 +1609,7 @@
         <v>29</v>
       </c>
       <c r="BC6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-28-2013-14</t>
+          <t>2014-01-28</t>
         </is>
       </c>
     </row>
@@ -1571,34 +1638,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E7" t="n">
         <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G7" t="n">
-        <v>0.356</v>
+        <v>0.364</v>
       </c>
       <c r="H7" t="n">
         <v>48.9</v>
       </c>
       <c r="I7" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J7" t="n">
-        <v>85.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0.424</v>
+        <v>0.425</v>
       </c>
       <c r="L7" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="M7" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="N7" t="n">
         <v>0.361</v>
@@ -1607,49 +1674,49 @@
         <v>16.4</v>
       </c>
       <c r="P7" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.74</v>
+        <v>0.743</v>
       </c>
       <c r="R7" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S7" t="n">
-        <v>31.9</v>
+        <v>32.1</v>
       </c>
       <c r="T7" t="n">
-        <v>44.4</v>
+        <v>44.6</v>
       </c>
       <c r="U7" t="n">
         <v>19.8</v>
       </c>
       <c r="V7" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W7" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X7" t="n">
         <v>4.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Z7" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AA7" t="n">
         <v>19.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>96.09999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>-5.2</v>
+        <v>-5.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
         <v>23</v>
@@ -1661,13 +1728,13 @@
         <v>23</v>
       </c>
       <c r="AH7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK7" t="n">
         <v>29</v>
@@ -1676,13 +1743,13 @@
         <v>21</v>
       </c>
       <c r="AM7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AP7" t="n">
         <v>19</v>
@@ -1694,10 +1761,10 @@
         <v>5</v>
       </c>
       <c r="AS7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU7" t="n">
         <v>28</v>
@@ -1706,13 +1773,13 @@
         <v>12</v>
       </c>
       <c r="AW7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AY7" t="n">
         <v>26</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>27</v>
       </c>
       <c r="AZ7" t="n">
         <v>8</v>
@@ -1721,7 +1788,7 @@
         <v>21</v>
       </c>
       <c r="BB7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC7" t="n">
         <v>25</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-28-2013-14</t>
+          <t>2014-01-28</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>1.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1843,7 +1910,7 @@
         <v>10</v>
       </c>
       <c r="AH8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI8" t="n">
         <v>3</v>
@@ -1864,7 +1931,7 @@
         <v>6</v>
       </c>
       <c r="AO8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP8" t="n">
         <v>27</v>
@@ -1876,7 +1943,7 @@
         <v>24</v>
       </c>
       <c r="AS8" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AT8" t="n">
         <v>29</v>
@@ -1891,19 +1958,19 @@
         <v>1</v>
       </c>
       <c r="AX8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY8" t="n">
         <v>3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC8" t="n">
         <v>12</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-28-2013-14</t>
+          <t>2014-01-28</t>
         </is>
       </c>
     </row>
@@ -2013,10 +2080,10 @@
         <v>0.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AE9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF9" t="n">
         <v>12</v>
@@ -2028,22 +2095,22 @@
         <v>30</v>
       </c>
       <c r="AI9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK9" t="n">
         <v>13</v>
       </c>
       <c r="AL9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM9" t="n">
         <v>9</v>
       </c>
       <c r="AN9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO9" t="n">
         <v>6</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-28-2013-14</t>
+          <t>2014-01-28</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F10" t="n">
         <v>27</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4</v>
+        <v>0.386</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
@@ -2144,7 +2211,7 @@
         <v>5.9</v>
       </c>
       <c r="M10" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="N10" t="n">
         <v>0.307</v>
@@ -2153,19 +2220,19 @@
         <v>17.1</v>
       </c>
       <c r="P10" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.665</v>
+        <v>0.664</v>
       </c>
       <c r="R10" t="n">
         <v>14.4</v>
       </c>
       <c r="S10" t="n">
-        <v>30.3</v>
+        <v>30.1</v>
       </c>
       <c r="T10" t="n">
-        <v>44.7</v>
+        <v>44.5</v>
       </c>
       <c r="U10" t="n">
         <v>20.3</v>
@@ -2180,7 +2247,7 @@
         <v>5.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z10" t="n">
         <v>20.5</v>
@@ -2192,10 +2259,10 @@
         <v>99.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.1</v>
+        <v>-3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AE10" t="n">
         <v>21</v>
@@ -2210,13 +2277,13 @@
         <v>16</v>
       </c>
       <c r="AI10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL10" t="n">
         <v>28</v>
@@ -2240,19 +2307,19 @@
         <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AT10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX10" t="n">
         <v>9</v>
@@ -2270,7 +2337,7 @@
         <v>17</v>
       </c>
       <c r="BC10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-28-2013-14</t>
+          <t>2014-01-28</t>
         </is>
       </c>
     </row>
@@ -2299,64 +2366,64 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E11" t="n">
         <v>27</v>
       </c>
       <c r="F11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G11" t="n">
-        <v>0.587</v>
+        <v>0.6</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>39</v>
+        <v>39.2</v>
       </c>
       <c r="J11" t="n">
-        <v>84.59999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="K11" t="n">
-        <v>0.461</v>
+        <v>0.463</v>
       </c>
       <c r="L11" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="M11" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0.385</v>
+        <v>0.386</v>
       </c>
       <c r="O11" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="P11" t="n">
         <v>21.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.735</v>
+        <v>0.734</v>
       </c>
       <c r="R11" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S11" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="T11" t="n">
-        <v>46</v>
+        <v>45.9</v>
       </c>
       <c r="U11" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="V11" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="W11" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="X11" t="n">
         <v>5.1</v>
@@ -2365,37 +2432,37 @@
         <v>4.7</v>
       </c>
       <c r="Z11" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="AA11" t="n">
         <v>20</v>
       </c>
       <c r="AB11" t="n">
-        <v>103.6</v>
+        <v>104</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
       </c>
       <c r="AF11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH11" t="n">
         <v>17</v>
       </c>
       <c r="AI11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>6</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>7</v>
       </c>
       <c r="AK11" t="n">
         <v>7</v>
@@ -2407,7 +2474,7 @@
         <v>6</v>
       </c>
       <c r="AN11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO11" t="n">
         <v>24</v>
@@ -2419,10 +2486,10 @@
         <v>23</v>
       </c>
       <c r="AR11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT11" t="n">
         <v>3</v>
@@ -2437,7 +2504,7 @@
         <v>13</v>
       </c>
       <c r="AX11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY11" t="n">
         <v>14</v>
@@ -2449,7 +2516,7 @@
         <v>19</v>
       </c>
       <c r="BB11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC11" t="n">
         <v>8</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-28-2013-14</t>
+          <t>2014-01-28</t>
         </is>
       </c>
     </row>
@@ -2481,55 +2548,55 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F12" t="n">
         <v>17</v>
       </c>
       <c r="G12" t="n">
-        <v>0.638</v>
+        <v>0.63</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="J12" t="n">
-        <v>79.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="K12" t="n">
-        <v>0.469</v>
+        <v>0.47</v>
       </c>
       <c r="L12" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="M12" t="n">
-        <v>26.2</v>
+        <v>26.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="O12" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="P12" t="n">
-        <v>31.4</v>
+        <v>31.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="S12" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="T12" t="n">
-        <v>45.1</v>
+        <v>44.9</v>
       </c>
       <c r="U12" t="n">
         <v>20.2</v>
@@ -2538,10 +2605,10 @@
         <v>16.1</v>
       </c>
       <c r="W12" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X12" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Y12" t="n">
         <v>5.6</v>
@@ -2550,16 +2617,16 @@
         <v>20.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>24.8</v>
+        <v>24.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>104.8</v>
+        <v>105</v>
       </c>
       <c r="AC12" t="n">
         <v>3.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
         <v>7</v>
@@ -2589,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO12" t="n">
         <v>1</v>
@@ -2601,16 +2668,16 @@
         <v>29</v>
       </c>
       <c r="AR12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AS12" t="n">
         <v>4</v>
       </c>
       <c r="AT12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV12" t="n">
         <v>28</v>
@@ -2622,10 +2689,10 @@
         <v>3</v>
       </c>
       <c r="AY12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-28-2013-14</t>
+          <t>2014-01-28</t>
         </is>
       </c>
     </row>
@@ -2663,67 +2730,67 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E13" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F13" t="n">
         <v>9</v>
       </c>
       <c r="G13" t="n">
-        <v>0.795</v>
+        <v>0.791</v>
       </c>
       <c r="H13" t="n">
         <v>48.2</v>
       </c>
       <c r="I13" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J13" t="n">
-        <v>80.8</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L13" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="M13" t="n">
         <v>19.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0.361</v>
+        <v>0.364</v>
       </c>
       <c r="O13" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="P13" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.777</v>
+        <v>0.783</v>
       </c>
       <c r="R13" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="S13" t="n">
-        <v>35.2</v>
+        <v>35</v>
       </c>
       <c r="T13" t="n">
-        <v>45.4</v>
+        <v>45</v>
       </c>
       <c r="U13" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V13" t="n">
-        <v>15.2</v>
+        <v>15.5</v>
       </c>
       <c r="W13" t="n">
         <v>7.2</v>
       </c>
       <c r="X13" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Y13" t="n">
         <v>4.4</v>
@@ -2732,16 +2799,16 @@
         <v>20.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>98.7</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="AE13" t="n">
         <v>2</v>
@@ -2762,25 +2829,25 @@
         <v>27</v>
       </c>
       <c r="AK13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AM13" t="n">
         <v>22</v>
       </c>
       <c r="AN13" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AO13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR13" t="n">
         <v>22</v>
@@ -2789,16 +2856,16 @@
         <v>1</v>
       </c>
       <c r="AT13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU13" t="n">
         <v>19</v>
       </c>
       <c r="AV13" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AW13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX13" t="n">
         <v>5</v>
@@ -2807,13 +2874,13 @@
         <v>10</v>
       </c>
       <c r="AZ13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA13" t="n">
         <v>6</v>
       </c>
       <c r="BB13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC13" t="n">
         <v>1</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-28-2013-14</t>
+          <t>2014-01-28</t>
         </is>
       </c>
     </row>
@@ -2935,13 +3002,13 @@
         <v>6</v>
       </c>
       <c r="AH14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI14" t="n">
         <v>10</v>
       </c>
       <c r="AJ14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK14" t="n">
         <v>6</v>
@@ -2971,13 +3038,13 @@
         <v>12</v>
       </c>
       <c r="AT14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU14" t="n">
         <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-28-2013-14</t>
+          <t>2014-01-28</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E15" t="n">
         <v>16</v>
       </c>
       <c r="F15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G15" t="n">
-        <v>0.348</v>
+        <v>0.356</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
@@ -3045,25 +3112,25 @@
         <v>37.1</v>
       </c>
       <c r="J15" t="n">
-        <v>84</v>
+        <v>83.8</v>
       </c>
       <c r="K15" t="n">
-        <v>0.441</v>
+        <v>0.443</v>
       </c>
       <c r="L15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M15" t="n">
         <v>24.9</v>
       </c>
       <c r="N15" t="n">
-        <v>0.37</v>
+        <v>0.373</v>
       </c>
       <c r="O15" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="P15" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="Q15" t="n">
         <v>0.755</v>
@@ -3072,16 +3139,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>32.9</v>
+        <v>32.6</v>
       </c>
       <c r="T15" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="U15" t="n">
         <v>22.5</v>
       </c>
       <c r="V15" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W15" t="n">
         <v>6.5</v>
@@ -3090,31 +3157,31 @@
         <v>5.6</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z15" t="n">
         <v>20.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>100.6</v>
+        <v>100.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.5</v>
+        <v>-5.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE15" t="n">
         <v>23</v>
       </c>
       <c r="AF15" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH15" t="n">
         <v>27</v>
@@ -3123,7 +3190,7 @@
         <v>19</v>
       </c>
       <c r="AJ15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK15" t="n">
         <v>20</v>
@@ -3141,7 +3208,7 @@
         <v>16</v>
       </c>
       <c r="AP15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ15" t="n">
         <v>17</v>
@@ -3150,25 +3217,25 @@
         <v>23</v>
       </c>
       <c r="AS15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU15" t="n">
         <v>11</v>
       </c>
       <c r="AV15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW15" t="n">
         <v>28</v>
       </c>
       <c r="AX15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ15" t="n">
         <v>12</v>
@@ -3177,7 +3244,7 @@
         <v>25</v>
       </c>
       <c r="BB15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC15" t="n">
         <v>26</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-28-2013-14</t>
+          <t>2014-01-28</t>
         </is>
       </c>
     </row>
@@ -3209,58 +3276,58 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F16" t="n">
         <v>20</v>
       </c>
       <c r="G16" t="n">
-        <v>0.535</v>
+        <v>0.524</v>
       </c>
       <c r="H16" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J16" t="n">
         <v>82.8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L16" t="n">
         <v>5.1</v>
       </c>
       <c r="M16" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0.353</v>
+        <v>0.351</v>
       </c>
       <c r="O16" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="P16" t="n">
-        <v>20.7</v>
+        <v>21</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.748</v>
+        <v>0.75</v>
       </c>
       <c r="R16" t="n">
         <v>12.1</v>
       </c>
       <c r="S16" t="n">
-        <v>31.3</v>
+        <v>31.1</v>
       </c>
       <c r="T16" t="n">
         <v>43.3</v>
       </c>
       <c r="U16" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V16" t="n">
         <v>13.5</v>
@@ -3272,25 +3339,25 @@
         <v>4.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z16" t="n">
         <v>19.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AF16" t="n">
         <v>10</v>
@@ -3302,13 +3369,13 @@
         <v>15</v>
       </c>
       <c r="AI16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ16" t="n">
         <v>15</v>
       </c>
       <c r="AK16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3323,16 +3390,16 @@
         <v>27</v>
       </c>
       <c r="AP16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ16" t="n">
         <v>20</v>
       </c>
       <c r="AR16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT16" t="n">
         <v>15</v>
@@ -3347,22 +3414,22 @@
         <v>18</v>
       </c>
       <c r="AX16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ16" t="n">
         <v>7</v>
       </c>
       <c r="BA16" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BB16" t="n">
         <v>25</v>
       </c>
       <c r="BC16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-28-2013-14</t>
+          <t>2014-01-28</t>
         </is>
       </c>
     </row>
@@ -3469,22 +3536,22 @@
         <v>5.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
         <v>5</v>
       </c>
       <c r="AF17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH17" t="n">
         <v>8</v>
       </c>
       <c r="AI17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3508,13 +3575,13 @@
         <v>12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
       </c>
       <c r="AS17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
@@ -3529,7 +3596,7 @@
         <v>4</v>
       </c>
       <c r="AX17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-28-2013-14</t>
+          <t>2014-01-28</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-9.800000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3663,7 +3730,7 @@
         <v>30</v>
       </c>
       <c r="AH18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI18" t="n">
         <v>29</v>
@@ -3711,7 +3778,7 @@
         <v>25</v>
       </c>
       <c r="AX18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY18" t="n">
         <v>19</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-28-2013-14</t>
+          <t>2014-01-28</t>
         </is>
       </c>
     </row>
@@ -3833,10 +3900,10 @@
         <v>4.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF19" t="n">
         <v>15</v>
@@ -3845,7 +3912,7 @@
         <v>15</v>
       </c>
       <c r="AH19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI19" t="n">
         <v>8</v>
@@ -3899,7 +3966,7 @@
         <v>24</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA19" t="n">
         <v>3</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-28-2013-14</t>
+          <t>2014-01-28</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F20" t="n">
         <v>25</v>
       </c>
       <c r="G20" t="n">
-        <v>0.432</v>
+        <v>0.419</v>
       </c>
       <c r="H20" t="n">
         <v>48.5</v>
@@ -3955,19 +4022,19 @@
         <v>38.4</v>
       </c>
       <c r="J20" t="n">
-        <v>84.09999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="K20" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L20" t="n">
         <v>6.1</v>
       </c>
       <c r="M20" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0.386</v>
+        <v>0.387</v>
       </c>
       <c r="O20" t="n">
         <v>17.8</v>
@@ -3976,49 +4043,49 @@
         <v>23.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.769</v>
+        <v>0.768</v>
       </c>
       <c r="R20" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="S20" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="T20" t="n">
         <v>42.8</v>
       </c>
       <c r="U20" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V20" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="W20" t="n">
         <v>8.5</v>
       </c>
       <c r="X20" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB20" t="n">
         <v>100.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>-1.6</v>
+        <v>-1.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="AE20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF20" t="n">
         <v>19</v>
@@ -4036,7 +4103,7 @@
         <v>9</v>
       </c>
       <c r="AK20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL20" t="n">
         <v>26</v>
@@ -4045,7 +4112,7 @@
         <v>29</v>
       </c>
       <c r="AN20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO20" t="n">
         <v>14</v>
@@ -4069,10 +4136,10 @@
         <v>14</v>
       </c>
       <c r="AV20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX20" t="n">
         <v>1</v>
@@ -4081,13 +4148,13 @@
         <v>28</v>
       </c>
       <c r="AZ20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA20" t="n">
         <v>18</v>
       </c>
       <c r="BB20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC20" t="n">
         <v>18</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-28-2013-14</t>
+          <t>2014-01-28</t>
         </is>
       </c>
     </row>
@@ -4119,64 +4186,64 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F21" t="n">
         <v>27</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4</v>
+        <v>0.386</v>
       </c>
       <c r="H21" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I21" t="n">
-        <v>36.5</v>
+        <v>36.3</v>
       </c>
       <c r="J21" t="n">
         <v>83.09999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.439</v>
+        <v>0.437</v>
       </c>
       <c r="L21" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="N21" t="n">
-        <v>0.364</v>
+        <v>0.361</v>
       </c>
       <c r="O21" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="P21" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.759</v>
+        <v>0.761</v>
       </c>
       <c r="R21" t="n">
         <v>10.9</v>
       </c>
       <c r="S21" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="T21" t="n">
-        <v>40.6</v>
+        <v>40.5</v>
       </c>
       <c r="U21" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V21" t="n">
         <v>12.7</v>
       </c>
       <c r="W21" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X21" t="n">
         <v>4.6</v>
@@ -4185,19 +4252,19 @@
         <v>3.8</v>
       </c>
       <c r="Z21" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>96.59999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.5</v>
+        <v>-3.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AE21" t="n">
         <v>21</v>
@@ -4209,16 +4276,16 @@
         <v>21</v>
       </c>
       <c r="AH21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI21" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AJ21" t="n">
         <v>14</v>
       </c>
       <c r="AK21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL21" t="n">
         <v>7</v>
@@ -4227,7 +4294,7 @@
         <v>8</v>
       </c>
       <c r="AN21" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AO21" t="n">
         <v>28</v>
@@ -4242,13 +4309,13 @@
         <v>20</v>
       </c>
       <c r="AS21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT21" t="n">
         <v>27</v>
       </c>
       <c r="AU21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
@@ -4257,22 +4324,22 @@
         <v>12</v>
       </c>
       <c r="AX21" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AY21" t="n">
         <v>5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BC21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-28-2013-14</t>
+          <t>2014-01-28</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>7.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4394,7 +4461,7 @@
         <v>25</v>
       </c>
       <c r="AI22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ22" t="n">
         <v>17</v>
@@ -4403,7 +4470,7 @@
         <v>4</v>
       </c>
       <c r="AL22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM22" t="n">
         <v>20</v>
@@ -4424,7 +4491,7 @@
         <v>15</v>
       </c>
       <c r="AS22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT22" t="n">
         <v>2</v>
@@ -4442,7 +4509,7 @@
         <v>2</v>
       </c>
       <c r="AY22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ22" t="n">
         <v>23</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-28-2013-14</t>
+          <t>2014-01-28</t>
         </is>
       </c>
     </row>
@@ -4483,25 +4550,25 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E23" t="n">
         <v>12</v>
       </c>
       <c r="F23" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G23" t="n">
-        <v>0.261</v>
+        <v>0.267</v>
       </c>
       <c r="H23" t="n">
         <v>48.8</v>
       </c>
       <c r="I23" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J23" t="n">
-        <v>82.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="K23" t="n">
         <v>0.443</v>
@@ -4513,16 +4580,16 @@
         <v>20.8</v>
       </c>
       <c r="N23" t="n">
-        <v>0.345</v>
+        <v>0.344</v>
       </c>
       <c r="O23" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="P23" t="n">
         <v>21.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.756</v>
+        <v>0.76</v>
       </c>
       <c r="R23" t="n">
         <v>9.1</v>
@@ -4531,16 +4598,16 @@
         <v>33.2</v>
       </c>
       <c r="T23" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U23" t="n">
         <v>20.5</v>
       </c>
       <c r="V23" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W23" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X23" t="n">
         <v>4.1</v>
@@ -4552,16 +4619,16 @@
         <v>20.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.3</v>
+        <v>96.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.9</v>
+        <v>-5.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4573,25 +4640,25 @@
         <v>29</v>
       </c>
       <c r="AH23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ23" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AK23" t="n">
         <v>19</v>
       </c>
       <c r="AL23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM23" t="n">
         <v>17</v>
       </c>
       <c r="AN23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO23" t="n">
         <v>20</v>
@@ -4600,10 +4667,10 @@
         <v>22</v>
       </c>
       <c r="AQ23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS23" t="n">
         <v>8</v>
@@ -4618,22 +4685,22 @@
         <v>19</v>
       </c>
       <c r="AW23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY23" t="n">
         <v>26</v>
       </c>
       <c r="AZ23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA23" t="n">
         <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC23" t="n">
         <v>27</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-28-2013-14</t>
+          <t>2014-01-28</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-8.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4755,7 +4822,7 @@
         <v>28</v>
       </c>
       <c r="AH24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI24" t="n">
         <v>7</v>
@@ -4788,7 +4855,7 @@
         <v>11</v>
       </c>
       <c r="AS24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT24" t="n">
         <v>9</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-28-2013-14</t>
+          <t>2014-01-28</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>3.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE25" t="n">
         <v>9</v>
@@ -4934,10 +5001,10 @@
         <v>8</v>
       </c>
       <c r="AG25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI25" t="n">
         <v>9</v>
@@ -4946,7 +5013,7 @@
         <v>8</v>
       </c>
       <c r="AK25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL25" t="n">
         <v>3</v>
@@ -4997,7 +5064,7 @@
         <v>11</v>
       </c>
       <c r="BB25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-28-2013-14</t>
+          <t>2014-01-28</t>
         </is>
       </c>
     </row>
@@ -5029,37 +5096,37 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E26" t="n">
         <v>33</v>
       </c>
       <c r="F26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G26" t="n">
-        <v>0.717</v>
+        <v>0.733</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>40.1</v>
+        <v>40.3</v>
       </c>
       <c r="J26" t="n">
         <v>88.5</v>
       </c>
       <c r="K26" t="n">
-        <v>0.453</v>
+        <v>0.455</v>
       </c>
       <c r="L26" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M26" t="n">
         <v>25.1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.383</v>
+        <v>0.388</v>
       </c>
       <c r="O26" t="n">
         <v>18.7</v>
@@ -5068,19 +5135,19 @@
         <v>22.7</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.821</v>
+        <v>0.822</v>
       </c>
       <c r="R26" t="n">
         <v>13.1</v>
       </c>
       <c r="S26" t="n">
-        <v>33.5</v>
+        <v>33.6</v>
       </c>
       <c r="T26" t="n">
-        <v>46.6</v>
+        <v>46.7</v>
       </c>
       <c r="U26" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="V26" t="n">
         <v>13.6</v>
@@ -5092,31 +5159,31 @@
         <v>4.7</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AA26" t="n">
         <v>20.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>108.4</v>
+        <v>109</v>
       </c>
       <c r="AC26" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE26" t="n">
         <v>3</v>
       </c>
       <c r="AF26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH26" t="n">
         <v>17</v>
@@ -5128,7 +5195,7 @@
         <v>3</v>
       </c>
       <c r="AK26" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AL26" t="n">
         <v>1</v>
@@ -5137,7 +5204,7 @@
         <v>4</v>
       </c>
       <c r="AN26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AO26" t="n">
         <v>9</v>
@@ -5173,7 +5240,7 @@
         <v>4</v>
       </c>
       <c r="AZ26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA26" t="n">
         <v>17</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-28-2013-14</t>
+          <t>2014-01-28</t>
         </is>
       </c>
     </row>
@@ -5289,28 +5356,28 @@
         <v>-2.7</v>
       </c>
       <c r="AD27" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE27" t="n">
         <v>26</v>
       </c>
       <c r="AF27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG27" t="n">
         <v>26</v>
       </c>
       <c r="AH27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AK27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL27" t="n">
         <v>22</v>
@@ -5328,13 +5395,13 @@
         <v>5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR27" t="n">
         <v>8</v>
       </c>
       <c r="AS27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT27" t="n">
         <v>12</v>
@@ -5364,7 +5431,7 @@
         <v>13</v>
       </c>
       <c r="BC27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-28-2013-14</t>
+          <t>2014-01-28</t>
         </is>
       </c>
     </row>
@@ -5393,55 +5460,55 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E28" t="n">
         <v>33</v>
       </c>
       <c r="F28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G28" t="n">
-        <v>0.733</v>
+        <v>0.75</v>
       </c>
       <c r="H28" t="n">
         <v>48.1</v>
       </c>
       <c r="I28" t="n">
-        <v>40.6</v>
+        <v>40.8</v>
       </c>
       <c r="J28" t="n">
         <v>82.5</v>
       </c>
       <c r="K28" t="n">
-        <v>0.493</v>
+        <v>0.494</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
         <v>20.5</v>
       </c>
       <c r="N28" t="n">
-        <v>0.402</v>
+        <v>0.406</v>
       </c>
       <c r="O28" t="n">
         <v>14.8</v>
       </c>
       <c r="P28" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.766</v>
+        <v>0.768</v>
       </c>
       <c r="R28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="S28" t="n">
-        <v>33.6</v>
+        <v>33.7</v>
       </c>
       <c r="T28" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="U28" t="n">
         <v>25.2</v>
@@ -5456,22 +5523,22 @@
         <v>4.8</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.8</v>
+        <v>17.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>104.4</v>
+        <v>104.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
@@ -5495,7 +5562,7 @@
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AM28" t="n">
         <v>18</v>
@@ -5504,16 +5571,16 @@
         <v>1</v>
       </c>
       <c r="AO28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP28" t="n">
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AR28" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS28" t="n">
         <v>5</v>
@@ -5531,19 +5598,19 @@
         <v>14</v>
       </c>
       <c r="AX28" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AY28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC28" t="n">
         <v>2</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-28-2013-14</t>
+          <t>2014-01-28</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>2.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE29" t="n">
         <v>11</v>
@@ -5671,13 +5738,13 @@
         <v>25</v>
       </c>
       <c r="AJ29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM29" t="n">
         <v>10</v>
@@ -5716,7 +5783,7 @@
         <v>22</v>
       </c>
       <c r="AY29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ29" t="n">
         <v>26</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-28-2013-14</t>
+          <t>2014-01-28</t>
         </is>
       </c>
     </row>
@@ -5835,16 +5902,16 @@
         <v>-6.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AE30" t="n">
         <v>23</v>
       </c>
       <c r="AF30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH30" t="n">
         <v>24</v>
@@ -5877,7 +5944,7 @@
         <v>18</v>
       </c>
       <c r="AR30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS30" t="n">
         <v>23</v>
@@ -5886,7 +5953,7 @@
         <v>24</v>
       </c>
       <c r="AU30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV30" t="n">
         <v>13</v>
@@ -5895,7 +5962,7 @@
         <v>27</v>
       </c>
       <c r="AX30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY30" t="n">
         <v>18</v>
@@ -5904,7 +5971,7 @@
         <v>18</v>
       </c>
       <c r="BA30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB30" t="n">
         <v>26</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-28-2013-14</t>
+          <t>2014-01-28</t>
         </is>
       </c>
     </row>
@@ -5939,61 +6006,61 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F31" t="n">
         <v>22</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5</v>
+        <v>0.488</v>
       </c>
       <c r="H31" t="n">
         <v>48.8</v>
       </c>
       <c r="I31" t="n">
-        <v>37.6</v>
+        <v>37.7</v>
       </c>
       <c r="J31" t="n">
-        <v>84</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.447</v>
+        <v>0.449</v>
       </c>
       <c r="L31" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="M31" t="n">
         <v>20.4</v>
       </c>
       <c r="N31" t="n">
-        <v>0.382</v>
+        <v>0.38</v>
       </c>
       <c r="O31" t="n">
-        <v>15.7</v>
+        <v>15.9</v>
       </c>
       <c r="P31" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.732</v>
+        <v>0.733</v>
       </c>
       <c r="R31" t="n">
         <v>11.1</v>
       </c>
       <c r="S31" t="n">
-        <v>32</v>
+        <v>31.7</v>
       </c>
       <c r="T31" t="n">
-        <v>43.1</v>
+        <v>42.8</v>
       </c>
       <c r="U31" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="V31" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W31" t="n">
         <v>8.5</v>
@@ -6002,46 +6069,46 @@
         <v>4.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA31" t="n">
         <v>19.4</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.7</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="AD31" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE31" t="n">
         <v>17</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>14</v>
       </c>
       <c r="AF31" t="n">
         <v>15</v>
       </c>
       <c r="AG31" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AH31" t="n">
         <v>3</v>
       </c>
       <c r="AI31" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AJ31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK31" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AL31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM31" t="n">
         <v>19</v>
@@ -6059,28 +6126,28 @@
         <v>24</v>
       </c>
       <c r="AR31" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS31" t="n">
         <v>17</v>
       </c>
-      <c r="AS31" t="n">
-        <v>15</v>
-      </c>
       <c r="AT31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU31" t="n">
         <v>9</v>
       </c>
       <c r="AV31" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AW31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ31" t="n">
         <v>16</v>
@@ -6089,7 +6156,7 @@
         <v>24</v>
       </c>
       <c r="BB31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC31" t="n">
         <v>17</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-28-2013-14</t>
+          <t>2014-01-28</t>
         </is>
       </c>
     </row>
